--- a/schemas/Физическая схема.xlsx
+++ b/schemas/Физическая схема.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="11955"/>
+    <workbookView windowWidth="30540" windowHeight="11955"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="78">
   <si>
     <t>Услуга (Service)</t>
   </si>
@@ -86,6 +86,9 @@
     <t>VARCHAR(20)</t>
   </si>
   <si>
+    <t>NOT NULL UNIQUE, CHECK (PHONE_NO ~ '^+7[0-9]{10}$')</t>
+  </si>
+  <si>
     <t>BASE_PRICE</t>
   </si>
   <si>
@@ -173,7 +176,7 @@
     <t>Дата и время записи</t>
   </si>
   <si>
-    <t>DATETIME</t>
+    <t>TIMESTAMP</t>
   </si>
   <si>
     <t>MASTER_EARNING</t>
@@ -430,7 +433,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,12 +508,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -620,12 +617,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -838,70 +829,70 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1346,70 +1337,70 @@
         <v>18</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1443,10 +1434,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>8</v>
@@ -1455,16 +1446,16 @@
         <v>9</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1478,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>6</v>
@@ -1490,98 +1481,98 @@
         <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1615,10 +1606,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>8</v>
@@ -1627,10 +1618,10 @@
         <v>9</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
@@ -1641,80 +1632,80 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
